--- a/builds.xlsx
+++ b/builds.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="367">
   <si>
     <t>Category</t>
   </si>
@@ -79,7 +79,7 @@
     <t>https://i.imgur.com/B0XcwPF.jpeg</t>
   </si>
   <si>
-    <t>#00E0FF</t>
+    <t>#590d22</t>
   </si>
   <si>
     <t>Suppressed build... this cannot 1 tap wallbang.</t>
@@ -92,18 +92,1037 @@
   </si>
   <si>
     <t>https://i.imgur.com/mNN5opt.jpeg</t>
+  </si>
+  <si>
+    <t>M21 EBR</t>
+  </si>
+  <si>
+    <t>RTC Compensator</t>
+  </si>
+  <si>
+    <t>MIP Steady</t>
+  </si>
+  <si>
+    <t>MIP Strike Stock</t>
+  </si>
+  <si>
+    <t>Tactical Foregrip A</t>
+  </si>
+  <si>
+    <t>OWC Laser - Tactical</t>
+  </si>
+  <si>
+    <t>1D2C4D6A7E</t>
+  </si>
+  <si>
+    <t>Ranger Foregrip</t>
+  </si>
+  <si>
+    <t>20 Round Reload</t>
+  </si>
+  <si>
+    <t>1D2C4D7D8B</t>
+  </si>
+  <si>
+    <t>XPR-50</t>
+  </si>
+  <si>
+    <t>Monolithic Suppressor</t>
+  </si>
+  <si>
+    <t>RTC Long</t>
+  </si>
+  <si>
+    <t>4X Tactical Scope</t>
+  </si>
+  <si>
+    <t>YKM Ghost Stock</t>
+  </si>
+  <si>
+    <t>OWC Stopping Power Reload</t>
+  </si>
+  <si>
+    <t>1C2C3F4C8C</t>
+  </si>
+  <si>
+    <t>RTC CQB</t>
+  </si>
+  <si>
+    <t>No Stock</t>
+  </si>
+  <si>
+    <t>1C2A4A5A8C</t>
+  </si>
+  <si>
+    <t>KOSHKA</t>
+  </si>
+  <si>
+    <t>MIP Light Barrel (Short)</t>
+  </si>
+  <si>
+    <t>Mobility Stock</t>
+  </si>
+  <si>
+    <t>10 Round Extended Mag</t>
+  </si>
+  <si>
+    <t>Stippled Grip Tape</t>
+  </si>
+  <si>
+    <t>Fast Switch</t>
+  </si>
+  <si>
+    <t>2A4A5G8A9C</t>
+  </si>
+  <si>
+    <t>OWC Light Suppressor</t>
+  </si>
+  <si>
+    <t>Armor Piercer Mag</t>
+  </si>
+  <si>
+    <t>1B2A4A8C9C</t>
+  </si>
+  <si>
+    <t>RYTEC AMR</t>
+  </si>
+  <si>
+    <t>2A4B5A6A9C</t>
+  </si>
+  <si>
+    <t>25x59mm Explosive Mag</t>
+  </si>
+  <si>
+    <t>1B2A4A8B9C</t>
+  </si>
+  <si>
+    <t>NA-45</t>
+  </si>
+  <si>
+    <t>OWC Light Compensator</t>
+  </si>
+  <si>
+    <t>RTC Steady Stock</t>
+  </si>
+  <si>
+    <t>Light Trigger</t>
+  </si>
+  <si>
+    <t>High Explosive Ammo</t>
+  </si>
+  <si>
+    <t>Sleight of Hand</t>
+  </si>
+  <si>
+    <t>1C4C5A7G8C</t>
+  </si>
+  <si>
+    <t>DL Q33</t>
+  </si>
+  <si>
+    <t>MIP Light</t>
+  </si>
+  <si>
+    <t>YKM Combat Stock</t>
+  </si>
+  <si>
+    <t>Extended Mag A</t>
+  </si>
+  <si>
+    <t>1B2A4A5A8A</t>
+  </si>
+  <si>
+    <t>3X Tactical Scope C</t>
+  </si>
+  <si>
+    <t>1C3E4D7D8B</t>
+  </si>
+  <si>
+    <t>HDR</t>
+  </si>
+  <si>
+    <t>FTAC Stalker-Scout</t>
+  </si>
+  <si>
+    <t>7 Round Mags</t>
+  </si>
+  <si>
+    <t>1B4A5A6A8A</t>
+  </si>
+  <si>
+    <t>LW3-TUNDRA</t>
+  </si>
+  <si>
+    <t>Tactical Suppressor</t>
+  </si>
+  <si>
+    <t>28.2" Tiger Team</t>
+  </si>
+  <si>
+    <t>7 Rnd</t>
+  </si>
+  <si>
+    <t>Serpent Wrap</t>
+  </si>
+  <si>
+    <t>1A2F5A8A9E</t>
+  </si>
+  <si>
+    <t>26.5" Hammer Forged</t>
+  </si>
+  <si>
+    <t>Bandit Steady Stock</t>
+  </si>
+  <si>
+    <t>Striker Foregrip</t>
+  </si>
+  <si>
+    <t>2B4D7B8A9E</t>
+  </si>
+  <si>
+    <t>2F4D5A8A9E</t>
+  </si>
+  <si>
+    <t>3-LINE RIFLE</t>
+  </si>
+  <si>
+    <t>Quicksilver Silencer</t>
+  </si>
+  <si>
+    <t>Empress 514mm F01</t>
+  </si>
+  <si>
+    <t>ZAC Custom MZ</t>
+  </si>
+  <si>
+    <t>.30-06 20 Round Mags</t>
+  </si>
+  <si>
+    <t>1D2A4B5A8C</t>
+  </si>
+  <si>
+    <t>270mm VOZ Carbine</t>
+  </si>
+  <si>
+    <t>1D2F4B5A8C</t>
+  </si>
+  <si>
+    <t>Marksman</t>
+  </si>
+  <si>
+    <t>SO-14</t>
+  </si>
+  <si>
+    <t>Polarfire-S</t>
+  </si>
+  <si>
+    <t>16" Chrome-lined RFX40 Barrel</t>
+  </si>
+  <si>
+    <t>FTAC RTP-40 Stock</t>
+  </si>
+  <si>
+    <t>50 Round Drums</t>
+  </si>
+  <si>
+    <t>Disable</t>
+  </si>
+  <si>
+    <t>1C2D4A5D8B</t>
+  </si>
+  <si>
+    <t>#1b998b</t>
+  </si>
+  <si>
+    <t>FSS GEN.7 Grip</t>
+  </si>
+  <si>
+    <t>1C2D4A8B9B</t>
+  </si>
+  <si>
+    <t>1C2D4A5D9B</t>
+  </si>
+  <si>
+    <t>TYPE 63</t>
+  </si>
+  <si>
+    <t>GRU Silencer</t>
+  </si>
+  <si>
+    <t>16.4" Titanium</t>
+  </si>
+  <si>
+    <t>Spetsnaz Ergonomic Grip</t>
+  </si>
+  <si>
+    <t>Airborne Elastic Wrap</t>
+  </si>
+  <si>
+    <t>1B2B5A7E9F</t>
+  </si>
+  <si>
+    <t>Silencer</t>
+  </si>
+  <si>
+    <t>18.3" Strike Team</t>
+  </si>
+  <si>
+    <t>Bruiser Grip</t>
+  </si>
+  <si>
+    <t>1A2D5D7B9F</t>
+  </si>
+  <si>
+    <t>SP-R 208</t>
+  </si>
+  <si>
+    <t>.300 5 Round Reload</t>
+  </si>
+  <si>
+    <t>Light Bolt</t>
+  </si>
+  <si>
+    <t>2A4B6A8B9A</t>
+  </si>
+  <si>
+    <t>YKM Integral Suppressor Light</t>
+  </si>
+  <si>
+    <t>2D4B5A8B9A</t>
+  </si>
+  <si>
+    <t>SKS</t>
+  </si>
+  <si>
+    <t>MIP Extended Light Barrel</t>
+  </si>
+  <si>
+    <t>Granulated Grip Tape</t>
+  </si>
+  <si>
+    <t>1A2B5E7E9A</t>
+  </si>
+  <si>
+    <t>MIP Stalker Stock</t>
+  </si>
+  <si>
+    <t>Operator Foregrip</t>
+  </si>
+  <si>
+    <t>1A2A4C5E7C</t>
+  </si>
+  <si>
+    <t>1A2B4C7E9A</t>
+  </si>
+  <si>
+    <t>KILO BOLT-ACTION</t>
+  </si>
+  <si>
+    <t>4B5H6A8B9A</t>
+  </si>
+  <si>
+    <t>YKM Light Stock</t>
+  </si>
+  <si>
+    <t>2A4A5B8B9A</t>
+  </si>
+  <si>
+    <t>Thermite Reload</t>
+  </si>
+  <si>
+    <t>1A4B5H8C9C</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>AS VAL</t>
+  </si>
+  <si>
+    <t>MIP Quick Response Barrel</t>
+  </si>
+  <si>
+    <t>15 Round FMJ</t>
+  </si>
+  <si>
+    <t>2B4B5A8C9A</t>
+  </si>
+  <si>
+    <t>#d7263d</t>
+  </si>
+  <si>
+    <t>MIP 200mm Mid-Range Barrel</t>
+  </si>
+  <si>
+    <t>Large Extended Mag B</t>
+  </si>
+  <si>
+    <t>2C4B6C8A9A</t>
+  </si>
+  <si>
+    <t>DR-H</t>
+  </si>
+  <si>
+    <t>OWC Ranger</t>
+  </si>
+  <si>
+    <t>25 Round OTM Mag</t>
+  </si>
+  <si>
+    <t>1A2B4D8C9A</t>
+  </si>
+  <si>
+    <t>1A2B4A8C9A</t>
+  </si>
+  <si>
+    <t>HVK-30</t>
+  </si>
+  <si>
+    <t>OWC Marksman</t>
+  </si>
+  <si>
+    <t>Large Caliber Ammo</t>
+  </si>
+  <si>
+    <t>1C2B4B8C9A</t>
+  </si>
+  <si>
+    <t>1C2A4C8C9A</t>
+  </si>
+  <si>
+    <t>KN-44</t>
+  </si>
+  <si>
+    <t>38 Round Fast Reload</t>
+  </si>
+  <si>
+    <t>1C2B4A8B9A</t>
+  </si>
+  <si>
+    <t>MAN-O-WAR</t>
+  </si>
+  <si>
+    <t>Thermite Ammo</t>
+  </si>
+  <si>
+    <t>Wounding</t>
+  </si>
+  <si>
+    <t>1B2A5C8C9A</t>
+  </si>
+  <si>
+    <t>1B4C5C8C9A</t>
+  </si>
+  <si>
+    <t>ICR-1</t>
+  </si>
+  <si>
+    <t>MacroMag IFS</t>
+  </si>
+  <si>
+    <t>2C4A5A8D9A</t>
+  </si>
+  <si>
+    <t>LK24</t>
+  </si>
+  <si>
+    <t>50 Round Extended Mag</t>
+  </si>
+  <si>
+    <t>1A2B4D8B9A</t>
+  </si>
+  <si>
+    <t>1A2A4A8B9A</t>
+  </si>
+  <si>
+    <t>AK117</t>
+  </si>
+  <si>
+    <t>48 Round Extended Mag</t>
+  </si>
+  <si>
+    <t>XM4</t>
+  </si>
+  <si>
+    <t>Agency Suppressor</t>
+  </si>
+  <si>
+    <t>13.5" Task Force</t>
+  </si>
+  <si>
+    <t>SAS Combat Stock</t>
+  </si>
+  <si>
+    <t>SALVO 45 Rnd Fast Mag</t>
+  </si>
+  <si>
+    <t>1A2G4E8F9E</t>
+  </si>
+  <si>
+    <t>BP50</t>
+  </si>
+  <si>
+    <t>Maxim Silencer</t>
+  </si>
+  <si>
+    <t>LEROY 438mm Rapid</t>
+  </si>
+  <si>
+    <t>Removed Stock</t>
+  </si>
+  <si>
+    <t>7.62x54MMR 30 Round Mags</t>
+  </si>
+  <si>
+    <t>Stippled Grip</t>
+  </si>
+  <si>
+    <t>1D2C4A8C9H</t>
+  </si>
+  <si>
+    <t>LEROY Custom</t>
+  </si>
+  <si>
+    <t>.30 Russian Short 60 Round Drums</t>
+  </si>
+  <si>
+    <t>1D2C4B8B9H</t>
+  </si>
+  <si>
+    <t>TYPE 19</t>
+  </si>
+  <si>
+    <t>Agile Stock</t>
+  </si>
+  <si>
+    <t>Merc Foregrip</t>
+  </si>
+  <si>
+    <t>Fast Reload Mag</t>
+  </si>
+  <si>
+    <t>Polymer Grip</t>
+  </si>
+  <si>
+    <t>1A4A7B8B9C</t>
+  </si>
+  <si>
+    <t>Accurate/Supportive Long Barrel</t>
+  </si>
+  <si>
+    <t>1A2A4A7B8B</t>
+  </si>
+  <si>
+    <t>North-Industry Heavyweight Suppressor</t>
+  </si>
+  <si>
+    <t>1D2A4A8B9C</t>
+  </si>
+  <si>
+    <t>GRAU 5.56</t>
+  </si>
+  <si>
+    <t>Tempus 26.4" Archangel</t>
+  </si>
+  <si>
+    <t>50 Round Mags</t>
+  </si>
+  <si>
+    <t>Cronen Sniper Elite</t>
+  </si>
+  <si>
+    <t>1A2D4A8A9A</t>
+  </si>
+  <si>
+    <t>FFAR 1</t>
+  </si>
+  <si>
+    <t>19.5" Task Force</t>
+  </si>
+  <si>
+    <t>Salvo 44 Rnd Fast Mag</t>
+  </si>
+  <si>
+    <t>1B2F4F8E9E</t>
+  </si>
+  <si>
+    <t>20.3" Takedown</t>
+  </si>
+  <si>
+    <t>BO Foregrip</t>
+  </si>
+  <si>
+    <t>1B2E7C8E9E</t>
+  </si>
+  <si>
+    <t>Tactical Stock</t>
+  </si>
+  <si>
+    <t>Field Agent Foregrip</t>
+  </si>
+  <si>
+    <t>Speed Tape</t>
+  </si>
+  <si>
+    <t>2E4B7E8E9A</t>
+  </si>
+  <si>
+    <t>ODEN</t>
+  </si>
+  <si>
+    <t>1D4C6C7C9A</t>
+  </si>
+  <si>
+    <t>1D4B5A7C9A</t>
+  </si>
+  <si>
+    <t>KILO 141</t>
+  </si>
+  <si>
+    <t>1C4A6C8B9A</t>
+  </si>
+  <si>
+    <t>RAM-7</t>
+  </si>
+  <si>
+    <t>FORGE TAC Eclipse</t>
+  </si>
+  <si>
+    <t>XRK Ultralight Hollow</t>
+  </si>
+  <si>
+    <t>50 Round Reload</t>
+  </si>
+  <si>
+    <t>1A2B4B8A9A</t>
+  </si>
+  <si>
+    <t>SAS Mag Clamp</t>
+  </si>
+  <si>
+    <t>1A2G4E8E9E</t>
+  </si>
+  <si>
+    <t>STANAG 50 Rnd</t>
+  </si>
+  <si>
+    <t>1A2G7B8D9E</t>
+  </si>
+  <si>
+    <t>LMG</t>
+  </si>
+  <si>
+    <t>UL736</t>
+  </si>
+  <si>
+    <t>RTC 25.4" Extended Barrel</t>
+  </si>
+  <si>
+    <t>1A2B4C5D9A</t>
+  </si>
+  <si>
+    <t>#003566</t>
+  </si>
+  <si>
+    <t>HADES</t>
+  </si>
+  <si>
+    <t>RTC Muzzle Brake</t>
+  </si>
+  <si>
+    <t>Rapid Fire Barrel</t>
+  </si>
+  <si>
+    <t>Crossbar</t>
+  </si>
+  <si>
+    <t>Rustle Grip Tape</t>
+  </si>
+  <si>
+    <t>1F2B5E7A9A</t>
+  </si>
+  <si>
+    <t>HOLGER 26</t>
+  </si>
+  <si>
+    <t>1C2A4A5D9A</t>
+  </si>
+  <si>
+    <t>1A4A5D6C9A</t>
+  </si>
+  <si>
+    <t>1A4A5D7E9A</t>
+  </si>
+  <si>
+    <t>CHOPPER</t>
+  </si>
+  <si>
+    <t>Chopper Infantry</t>
+  </si>
+  <si>
+    <t>Heavy Handle</t>
+  </si>
+  <si>
+    <t>1C2B5E6C7G</t>
+  </si>
+  <si>
+    <t>RPD</t>
+  </si>
+  <si>
+    <t>Cooling Compressor Barrel</t>
+  </si>
+  <si>
+    <t>1C2D4D5A9A</t>
+  </si>
+  <si>
+    <t>2B4C6C8A9A</t>
+  </si>
+  <si>
+    <t>RAAL MG</t>
+  </si>
+  <si>
+    <t>RAAL Monocore</t>
+  </si>
+  <si>
+    <t>32.0" RAAL Line Breaker</t>
+  </si>
+  <si>
+    <t>Folded Stock</t>
+  </si>
+  <si>
+    <t>150 Round Belt</t>
+  </si>
+  <si>
+    <t>1C2B4B5A8A</t>
+  </si>
+  <si>
+    <t>MG42</t>
+  </si>
+  <si>
+    <t>VDD 682MM 31M</t>
+  </si>
+  <si>
+    <t>MK6 PARA</t>
+  </si>
+  <si>
+    <t>Leather Grip</t>
+  </si>
+  <si>
+    <t>1F2A5E7E9J</t>
+  </si>
+  <si>
+    <t>PKM</t>
+  </si>
+  <si>
+    <t>Snatch Foregrip</t>
+  </si>
+  <si>
+    <t>1C2C5A7E9A</t>
+  </si>
+  <si>
+    <t>SMG</t>
+  </si>
+  <si>
+    <t>QQ9</t>
+  </si>
+  <si>
+    <t>RTC Recon Tac Long</t>
+  </si>
+  <si>
+    <t>10mm 30 Round Reload</t>
+  </si>
+  <si>
+    <t>1C2C4A8C9A</t>
+  </si>
+  <si>
+    <t>#f46036</t>
+  </si>
+  <si>
+    <t>GKS</t>
+  </si>
+  <si>
+    <t>40 Round Extended Mag</t>
+  </si>
+  <si>
+    <t>1C2A6C8A9A</t>
+  </si>
+  <si>
+    <t>HG 40</t>
+  </si>
+  <si>
+    <t>YKM Integral Suppressor</t>
+  </si>
+  <si>
+    <t>45 Round Fast Reload</t>
+  </si>
+  <si>
+    <t>2C4A6C8C9A</t>
+  </si>
+  <si>
+    <t>PDW-57</t>
+  </si>
+  <si>
+    <t>1C2A4A5E9A</t>
+  </si>
+  <si>
+    <t>MAC-10</t>
+  </si>
+  <si>
+    <t>Taskforce Barrel</t>
+  </si>
+  <si>
+    <t>Steel Stock</t>
+  </si>
+  <si>
+    <t>43 Round Extended Reload</t>
+  </si>
+  <si>
+    <t>1B2A4B7B8A</t>
+  </si>
+  <si>
+    <t>CBR4</t>
+  </si>
+  <si>
+    <t>1A2B4A5E9A</t>
+  </si>
+  <si>
+    <t>1C2B4B5E9A</t>
+  </si>
+  <si>
+    <t>PP19 BIZON</t>
+  </si>
+  <si>
+    <t>Large Caliber Ammo A</t>
+  </si>
+  <si>
+    <t>1C2B4C6C8B</t>
+  </si>
+  <si>
+    <t>1C2A4C8B9A</t>
+  </si>
+  <si>
+    <t>FENNEC</t>
+  </si>
+  <si>
+    <t>1C2C4D7C8A</t>
+  </si>
+  <si>
+    <t>CX-9</t>
+  </si>
+  <si>
+    <t>CX-38S</t>
+  </si>
+  <si>
+    <t>CX-FR</t>
+  </si>
+  <si>
+    <t>9mm Hollow Point 12-R Mags</t>
+  </si>
+  <si>
+    <t>CX-9 Ace Grip</t>
+  </si>
+  <si>
+    <t>2D4A5B8C9A</t>
+  </si>
+  <si>
+    <t>CX-23</t>
+  </si>
+  <si>
+    <t>2E4A5B8C9A</t>
+  </si>
+  <si>
+    <t>2D4A5B8B9A</t>
+  </si>
+  <si>
+    <t>SWITCHBLADE X9</t>
+  </si>
+  <si>
+    <t>1A2C4B8A9A</t>
+  </si>
+  <si>
+    <t>1A2C5F8A9A</t>
+  </si>
+  <si>
+    <t>1C2C4A8A9A</t>
+  </si>
+  <si>
+    <t>43 Round Fast Reload</t>
+  </si>
+  <si>
+    <t>1B2A4D7B8D</t>
+  </si>
+  <si>
+    <t>VMP</t>
+  </si>
+  <si>
+    <t>Heavy Barrel</t>
+  </si>
+  <si>
+    <t>Removed Pad</t>
+  </si>
+  <si>
+    <t>VX Pineapple Grip (Lightweight)</t>
+  </si>
+  <si>
+    <t>Phoenix Grip Set</t>
+  </si>
+  <si>
+    <t>Rapid Fire</t>
+  </si>
+  <si>
+    <t>2D4D5H7B9B</t>
+  </si>
+  <si>
+    <t>Fast Extended Mag</t>
+  </si>
+  <si>
+    <t>2D5H7B8D9B</t>
+  </si>
+  <si>
+    <t>USS 9</t>
+  </si>
+  <si>
+    <t>FSS Carbine Pro</t>
+  </si>
+  <si>
+    <t>FORGE TAC Ultralight</t>
+  </si>
+  <si>
+    <t>.41 AE 32-Round Mags</t>
+  </si>
+  <si>
+    <t>1C2D4B8C9A</t>
+  </si>
+  <si>
+    <t>13.1" First Responder</t>
+  </si>
+  <si>
+    <t>1C2D4A8C9A</t>
+  </si>
+  <si>
+    <t>TEC-9</t>
+  </si>
+  <si>
+    <t>Burst Fire Repeater</t>
+  </si>
+  <si>
+    <t>8.1" Task Force</t>
+  </si>
+  <si>
+    <t>1G2F7B8A9F</t>
+  </si>
+  <si>
+    <t>Shotgun</t>
+  </si>
+  <si>
+    <t>JAK-12</t>
+  </si>
+  <si>
+    <t>Marauder Suppressor</t>
+  </si>
+  <si>
+    <t>MIP Laser 5mW</t>
+  </si>
+  <si>
+    <t>8-R Dragon's Breath</t>
+  </si>
+  <si>
+    <t>1C2B6B9A</t>
+  </si>
+  <si>
+    <t>#ffa62b</t>
+  </si>
+  <si>
+    <t>ARGUS</t>
+  </si>
+  <si>
+    <t>Choke</t>
+  </si>
+  <si>
+    <t>BO Barrel</t>
+  </si>
+  <si>
+    <t>Steady Stock</t>
+  </si>
+  <si>
+    <t>Classical Lever</t>
+  </si>
+  <si>
+    <t>Outlaw Mag</t>
+  </si>
+  <si>
+    <t>1D2A4E7C8C</t>
+  </si>
+  <si>
+    <t>BY15</t>
+  </si>
+  <si>
+    <t>RTC Extended Light Barrel</t>
+  </si>
+  <si>
+    <t>500gr Slug</t>
+  </si>
+  <si>
+    <t>1C2A4A6C8B</t>
+  </si>
+  <si>
+    <t>KRM-262</t>
+  </si>
+  <si>
+    <t>RTC Light Extended Barrel</t>
+  </si>
+  <si>
+    <t>Speed Up Kill</t>
+  </si>
+  <si>
+    <t>1C2A4A5E6B</t>
+  </si>
+  <si>
+    <t>1C2A4A6C9A</t>
+  </si>
+  <si>
+    <t>STRIKER</t>
+  </si>
+  <si>
+    <t>RTC Laser 1mW</t>
+  </si>
+  <si>
+    <t>16 Round Extended Reload Case</t>
+  </si>
+  <si>
+    <t>1A2B5A6A8A</t>
+  </si>
+  <si>
+    <t>RTC Retractable Barrel</t>
+  </si>
+  <si>
+    <t>Fast Reload Reload Case</t>
+  </si>
+  <si>
+    <t>1F2C6A8B9A</t>
+  </si>
+  <si>
+    <t>HS0405</t>
+  </si>
+  <si>
+    <t>1F2A4A6B9C</t>
+  </si>
+  <si>
+    <t>Thunder Rounds</t>
+  </si>
+  <si>
+    <t>1F2A4A6B8C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="M/d/yyyy H:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="MM/dd/yyyy HH:mm"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy h:mm"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy h:mm"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -118,6 +1137,15 @@
     <font>
       <u/>
       <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,7 +1162,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -147,10 +1175,14 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -370,8 +1402,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="2" max="2" width="18.5"/>
     <col customWidth="1" min="3" max="3" width="18.63"/>
-    <col customWidth="1" min="4" max="8" width="18.5"/>
+    <col customWidth="1" min="4" max="8" width="32.38"/>
     <col customWidth="1" min="9" max="9" width="13.13"/>
     <col customWidth="1" min="10" max="10" width="17.13"/>
   </cols>
@@ -449,7 +1482,7 @@
         <v>22</v>
       </c>
       <c r="L2" s="3">
-        <v>46120.54791666667</v>
+        <v>46120.77569444444</v>
       </c>
     </row>
     <row r="3">
@@ -487,20 +1520,3434 @@
         <v>22</v>
       </c>
       <c r="L3" s="3">
-        <v>46120.555555555555</v>
+        <v>46120.77569444444</v>
       </c>
     </row>
     <row r="4">
-      <c r="K4" s="4"/>
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="7">
+        <v>46120.76875</v>
+      </c>
     </row>
     <row r="7">
-      <c r="K7" s="4"/>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="7">
+        <v>46120.76875</v>
+      </c>
     </row>
     <row r="11">
-      <c r="L11" s="4"/>
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="7">
+        <v>46120.76875</v>
+      </c>
     </row>
     <row r="15">
-      <c r="L15" s="5"/>
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L21" s="7">
+        <v>46120.77361111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L22" s="7">
+        <v>46120.77361111111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L25" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L26" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L27" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L28" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L29" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L30" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L31" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L32" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L33" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L34" s="7">
+        <v>46120.77361111111</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L35" s="7">
+        <v>46120.77361111111</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L36" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L37" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L38" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L39" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L40" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L41" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L42" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L43" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L44" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L45" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L46" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L47" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L48" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L49" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L50" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L51" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L52" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L53" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L54" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L55" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L56" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L57" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C58" s="5"/>
+      <c r="D58" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L58" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L59" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L60" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L61" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L62" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="D63" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L63" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L64" s="7">
+        <v>46120.774305555555</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L65" s="7">
+        <v>46120.774305555555</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L66" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L67" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L68" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L69" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L70" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C71" s="5"/>
+      <c r="D71" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L71" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C72" s="5"/>
+      <c r="D72" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L72" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C73" s="5"/>
+      <c r="D73" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L73" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C74" s="5"/>
+      <c r="D74" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L74" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C75" s="5"/>
+      <c r="D75" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L75" s="7">
+        <v>46120.77291666667</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C76" s="5"/>
+      <c r="D76" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L76" s="7">
+        <v>46120.775</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C77" s="5"/>
+      <c r="D77" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L77" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C78" s="5"/>
+      <c r="D78" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L78" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C79" s="5"/>
+      <c r="D79" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L79" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C80" s="5"/>
+      <c r="D80" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L80" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C81" s="5"/>
+      <c r="D81" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L81" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C82" s="5"/>
+      <c r="D82" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L82" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C83" s="5"/>
+      <c r="D83" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L83" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C84" s="5"/>
+      <c r="D84" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L84" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C85" s="5"/>
+      <c r="D85" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L85" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C86" s="5"/>
+      <c r="D86" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L86" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C87" s="5"/>
+      <c r="D87" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L87" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C88" s="5"/>
+      <c r="D88" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L88" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C89" s="5"/>
+      <c r="D89" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L89" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C90" s="5"/>
+      <c r="D90" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L90" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C91" s="5"/>
+      <c r="D91" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L91" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C92" s="5"/>
+      <c r="D92" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L92" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C93" s="5"/>
+      <c r="D93" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L93" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C94" s="5"/>
+      <c r="D94" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L94" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C95" s="5"/>
+      <c r="D95" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L95" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C96" s="5"/>
+      <c r="D96" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L96" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C97" s="5"/>
+      <c r="D97" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L97" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C98" s="5"/>
+      <c r="D98" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L98" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C99" s="5"/>
+      <c r="D99" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L99" s="7">
+        <v>46120.775</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C100" s="5"/>
+      <c r="D100" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L100" s="7">
+        <v>46120.775</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C101" s="5"/>
+      <c r="D101" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L101" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C102" s="5"/>
+      <c r="D102" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L102" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C103" s="5"/>
+      <c r="D103" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L103" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C104" s="5"/>
+      <c r="D104" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L104" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C105" s="5"/>
+      <c r="D105" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L105" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C106" s="5"/>
+      <c r="D106" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L106" s="7">
+        <v>46120.76875</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C107" s="5"/>
+      <c r="D107" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L107" s="7">
+        <v>46120.76875</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
